--- a/data/availability/projects/inertia-egypt/jefaira.xlsx
+++ b/data/availability/projects/inertia-egypt/jefaira.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>delivery_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory for jefaira</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -587,7 +597,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2-4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +647,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2-4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +697,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2-4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +747,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>3.5-4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -787,7 +797,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>3.5-4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -837,7 +847,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>3.5-4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -887,7 +897,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -937,7 +947,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -987,7 +997,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1037,7 +1047,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1087,7 +1097,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1137,7 +1147,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1187,7 +1197,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1237,7 +1247,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1287,7 +1297,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1337,7 +1347,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1459,7 +1469,6 @@
       <c r="G2" t="n">
         <v>139</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Sea &amp; Landscape</t>
@@ -1470,7 +1479,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2-4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1516,7 +1525,6 @@
       <c r="G3" t="n">
         <v>168</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Sea &amp; Landscape</t>
@@ -1527,7 +1535,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2-4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1573,7 +1581,6 @@
       <c r="G4" t="n">
         <v>253</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Sea &amp; Landscape</t>
@@ -1584,7 +1591,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2-4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1630,7 +1637,6 @@
       <c r="G5" t="n">
         <v>91</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Sea &amp; Landscape</t>
@@ -1641,7 +1647,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>3.5-4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1687,7 +1693,6 @@
       <c r="G6" t="n">
         <v>103</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Sea &amp; Landscape</t>
@@ -1698,7 +1703,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>3.5-4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1744,7 +1749,6 @@
       <c r="G7" t="n">
         <v>164</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Sea &amp; Landscape</t>
@@ -1755,7 +1759,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>3.5-4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1801,7 +1805,6 @@
       <c r="G8" t="n">
         <v>101</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Sea &amp; Landscape</t>
@@ -1812,7 +1815,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1858,7 +1861,6 @@
       <c r="G9" t="n">
         <v>139</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Sea &amp; Landscape</t>
@@ -1869,7 +1871,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1915,7 +1917,6 @@
       <c r="G10" t="n">
         <v>169</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Sea &amp; Landscape</t>
@@ -1926,7 +1927,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1972,7 +1973,6 @@
       <c r="G11" t="n">
         <v>185</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Sea &amp; Landscape</t>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -2029,7 +2029,6 @@
       <c r="G12" t="n">
         <v>201</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Sea &amp; Landscape</t>
@@ -2040,7 +2039,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2086,7 +2085,6 @@
       <c r="G13" t="n">
         <v>84</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Sea &amp; Landscape</t>
@@ -2097,7 +2095,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2143,7 +2141,6 @@
       <c r="G14" t="n">
         <v>117</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Sea &amp; Landscape</t>
@@ -2154,7 +2151,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2200,7 +2197,6 @@
       <c r="G15" t="n">
         <v>169</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Sea &amp; Landscape</t>
@@ -2211,7 +2207,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2257,7 +2253,6 @@
       <c r="G16" t="n">
         <v>168</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Sea &amp; Landscape</t>
@@ -2268,7 +2263,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2314,7 +2309,6 @@
       <c r="G17" t="n">
         <v>191</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Sea &amp; Landscape</t>
@@ -2325,7 +2319,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
